--- a/output/pdf_financials_xlsx/CF.xlsx
+++ b/output/pdf_financials_xlsx/CF.xlsx
@@ -9380,19 +9380,19 @@
         </is>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-30.282</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-33.301</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-35.577</v>
       </c>
       <c r="T124" s="3" t="n">
-        <v>0</v>
+        <v>-38.348</v>
       </c>
       <c r="U124" s="3" t="n">
-        <v>0</v>
+        <v>-47.533</v>
       </c>
     </row>
     <row r="125">
@@ -9457,19 +9457,19 @@
         </is>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-30.282</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-33.301</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-35.577</v>
       </c>
       <c r="T125" s="3" t="n">
-        <v>0</v>
+        <v>-38.348</v>
       </c>
       <c r="U125" s="3" t="n">
-        <v>0</v>
+        <v>-47.533</v>
       </c>
     </row>
     <row r="126">
@@ -40684,7 +40684,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CF.xlsx
+++ b/output/pdf_financials_xlsx/CF.xlsx
@@ -8032,28 +8032,28 @@
         <v>23.986</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.555</v>
+        <v>40.907</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.555</v>
+        <v>51.679</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>60.359</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>52.363</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>61.305</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>51.9</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>40.322</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>95.357</v>
       </c>
       <c r="N107" s="1" t="inlineStr">
         <is>
@@ -8071,19 +8071,19 @@
         </is>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>146.827</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>59.495</v>
       </c>
       <c r="S107" s="3" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="T107" s="3" t="n">
-        <v>0</v>
+        <v>14.02</v>
       </c>
       <c r="U107" s="3" t="n">
-        <v>0</v>
+        <v>59.818</v>
       </c>
     </row>
     <row r="108">
@@ -8734,19 +8734,19 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-7.002</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-16.636</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-4.17</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.795</v>
       </c>
       <c r="N116" s="1" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-4.006</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>0</v>
+        <v>-1.969</v>
       </c>
       <c r="T116" s="3" t="n">
-        <v>0</v>
+        <v>-2.71</v>
       </c>
       <c r="U116" s="3" t="n">
-        <v>0</v>
+        <v>-0.434</v>
       </c>
     </row>
     <row r="117">
@@ -38198,7 +38198,11 @@
           <t>Share-based compensation expense 23</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -41016,7 +41020,11 @@
           <t>Purchase of intangible assets 13</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -43102,7 +43110,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -43216,7 +43228,11 @@
           <t>Share-based compensation expense 24</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -44668,7 +44684,11 @@
           <t>Purchase of intangible assets 15</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -45472,7 +45492,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -48038,7 +48062,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -48144,7 +48172,11 @@
           <t>Share-based compensation expense 22</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -50330,7 +50362,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -50436,7 +50472,11 @@
           <t>Share-based compensation expense 21</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -51104,7 +51144,11 @@
           <t>Proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -51778,7 +51822,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -52116,7 +52164,11 @@
           <t>Share-based compensation expense 20</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -53252,7 +53304,11 @@
           <t>Share-based compensation expense 18</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -53936,7 +53992,11 @@
           <t>Share-based compensation expense 19</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -56342,7 +56402,11 @@
           <t>Share-based compensation expense 17</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -58882,7 +58946,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
